--- a/data/trans_orig/P1804_2016_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1804_2016_2023-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51325</t>
+          <t>52493</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82542</t>
+          <t>83766</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96235</t>
+          <t>96805</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>137712</t>
+          <t>142384</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>213001</t>
+          <t>211563</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>671805</t>
+          <t>670581</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>703022</t>
+          <t>701854</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>856948</t>
+          <t>852276</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>898425</t>
+          <t>897855</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1536006</t>
+          <t>1537444</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90088</t>
+          <t>90710</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>130769</t>
+          <t>130645</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>142538</t>
+          <t>141969</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>191933</t>
+          <t>193034</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>244005</t>
+          <t>242640</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>307883</t>
+          <t>308481</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1945616</t>
+          <t>1945740</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1986297</t>
+          <t>1985675</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1796367</t>
+          <t>1795266</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1845762</t>
+          <t>1846331</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3756802</t>
+          <t>3756204</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3820680</t>
+          <t>3822045</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27398</t>
+          <t>26850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53947</t>
+          <t>49961</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52625</t>
+          <t>52078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85141</t>
+          <t>84979</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88516</t>
+          <t>88848</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131023</t>
+          <t>128682</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>492939</t>
+          <t>496925</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>519488</t>
+          <t>520036</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>463999</t>
+          <t>464161</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>496515</t>
+          <t>497062</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>965004</t>
+          <t>967345</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1007511</t>
+          <t>1007179</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,89%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>186671</t>
+          <t>186079</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>242537</t>
+          <t>240882</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>312726</t>
+          <t>314788</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>387905</t>
+          <t>392475</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>517507</t>
+          <t>518026</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>609393</t>
+          <t>611075</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3135081</t>
+          <t>3136736</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3190947</t>
+          <t>3191539</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3144195</t>
+          <t>3139625</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3219374</t>
+          <t>3217312</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6300325</t>
+          <t>6298643</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6392211</t>
+          <t>6391692</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -2329,32 +2329,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>31474</t>
+          <t>32241</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22605</t>
+          <t>22937</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41987</t>
+          <t>43776</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2364,32 +2364,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>63128</t>
+          <t>69261</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53067</t>
+          <t>58778</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73870</t>
+          <t>83919</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2399,32 +2399,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>94601</t>
+          <t>101502</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79983</t>
+          <t>87893</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109347</t>
+          <t>119017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -2442,32 +2442,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>483464</t>
+          <t>546288</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>472951</t>
+          <t>534753</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>492333</t>
+          <t>555592</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2477,32 +2477,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>691814</t>
+          <t>752181</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>681072</t>
+          <t>737523</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>701875</t>
+          <t>762664</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2512,32 +2512,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1175280</t>
+          <t>1298469</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1160534</t>
+          <t>1280954</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1189898</t>
+          <t>1312078</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -2555,17 +2555,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2590,17 +2590,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>754942</t>
+          <t>821442</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>754942</t>
+          <t>821442</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>754942</t>
+          <t>821442</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2625,17 +2625,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1269881</t>
+          <t>1399971</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1269881</t>
+          <t>1399971</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1269881</t>
+          <t>1399971</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2672,32 +2672,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>100630</t>
+          <t>119779</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72241</t>
+          <t>97211</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>131081</t>
+          <t>148859</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2707,32 +2707,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>137188</t>
+          <t>160611</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>96886</t>
+          <t>137638</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>166964</t>
+          <t>187142</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2742,32 +2742,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>237818</t>
+          <t>280390</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>189724</t>
+          <t>248036</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>280610</t>
+          <t>320026</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -2785,32 +2785,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2189697</t>
+          <t>2110787</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2159246</t>
+          <t>2081707</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2218086</t>
+          <t>2133355</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2820,32 +2820,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2097405</t>
+          <t>2004553</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2067629</t>
+          <t>1978022</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2137707</t>
+          <t>2027526</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2855,32 +2855,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4287102</t>
+          <t>4115341</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4244310</t>
+          <t>4075705</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4335196</t>
+          <t>4147695</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -2898,17 +2898,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2933,17 +2933,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2234593</t>
+          <t>2165164</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2234593</t>
+          <t>2165164</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2234593</t>
+          <t>2165164</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2968,17 +2968,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4524920</t>
+          <t>4395731</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4524920</t>
+          <t>4395731</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4524920</t>
+          <t>4395731</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3015,67 +3015,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>58730</t>
+          <t>66547</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45870</t>
+          <t>51431</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76839</t>
+          <t>88623</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>12,45%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>87294</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>72315</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>103412</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>11,88%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>75828</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>62634</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>90449</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>11,48%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3085,32 +3085,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>134558</t>
+          <t>153841</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>112143</t>
+          <t>129351</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157441</t>
+          <t>179083</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -3128,67 +3128,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>587893</t>
+          <t>645040</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>569784</t>
+          <t>622964</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>600753</t>
+          <t>660156</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>87,55%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,77%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>647583</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>631465</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>662562</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>88,12%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>92,91%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>890</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>584635</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>570014</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>597829</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>88,52%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3198,32 +3198,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1172528</t>
+          <t>1292623</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1149645</t>
+          <t>1267381</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1194943</t>
+          <t>1317113</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -3241,17 +3241,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3276,17 +3276,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3358,32 +3358,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>190834</t>
+          <t>218567</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>152204</t>
+          <t>188856</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>224556</t>
+          <t>255424</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3393,32 +3393,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>276144</t>
+          <t>317166</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>228044</t>
+          <t>288762</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>314905</t>
+          <t>351620</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3428,32 +3428,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>466978</t>
+          <t>535733</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>398721</t>
+          <t>493441</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>519274</t>
+          <t>585210</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -3471,32 +3471,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3261055</t>
+          <t>3302116</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3227333</t>
+          <t>3265259</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3299685</t>
+          <t>3331827</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3373854</t>
+          <t>3404317</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3335093</t>
+          <t>3369863</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3421954</t>
+          <t>3432721</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6634909</t>
+          <t>6706433</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6582613</t>
+          <t>6656956</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6703166</t>
+          <t>6748725</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -3584,17 +3584,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3619,17 +3619,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649998</t>
+          <t>3721483</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649998</t>
+          <t>3721483</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649998</t>
+          <t>3721483</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3654,17 +3654,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7101887</t>
+          <t>7242166</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7101887</t>
+          <t>7242166</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7101887</t>
+          <t>7242166</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
